--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/14 11:52:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14 10:06:33</t>
+          <t>09/17 09:12:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/14 11:52:43</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>119000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>14000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>14000</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/17 11:35:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>119000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>119000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14000</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 09:12:28</t>
+          <t>09/18 11:55:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/17 11:35:17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14000</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/18 14:31:58</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 11:55:15</t>
+          <t>09/21 14:18:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/18 14:31:58</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>12941.18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>12941.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/21 14:18:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12941.18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12941.18</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12653.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/21 15:47:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12653</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/21 14:18:50</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>12941.18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12941</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>12653.18</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 14:18:40</t>
+          <t>09/22 19:08:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/21 15:47:11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12653</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21 14:18:50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12941.18</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>12941</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.18</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/22 19:11:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11376.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/22 19:12:35</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/22 19:11:34</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11376.71</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6376.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
+          <t>09/22 20:12:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -229,83 +229,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/22 19:12:35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/22 19:11:34</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6376.71</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 19:08:39</t>
+          <t>09/23 12:36:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,140 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/22 20:12:06</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6376</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22 19:12:35</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22 19:11:34</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11764.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -72,186 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/23 12:36:02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>11904.76</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/23 12:37:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>110000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13095.24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13095.24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13095.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/23 13:35:49</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20481.93</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/23 12:37:12</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>110000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>13095.24</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33577.17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13095.24</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>33577.17</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/23 14:50:17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>33577</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>33577.17</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33577.17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>33577</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>33577.17</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.17</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 13:35:49</t>
+          <t>09/25 13:17:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>12941.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/23 12:37:12</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>13095.24</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 14:50:17</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>33577</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>110000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12941.18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33577.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>33577</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.17</t>
+          <t>12941.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/25 15:00:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12941</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12941.18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12941</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12941.18</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.18</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 13:17:56</t>
+          <t>09/27 10:35:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>19047.62</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/25 15:00:33</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12941</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>19047.62</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12941.18</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12941</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.18</t>
+          <t>19047.62</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/27 12:36:22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19047</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19047.62</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19047</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19047.62</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.62</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/27 10:35:25</t>
+          <t>09/28 14:40:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>260000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>31515.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/27 12:36:22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>19047</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>31515.15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19047</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.62</t>
+          <t>31515.15</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/28 18:19:39</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>31515</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>260000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31515.15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>31515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>31515.15</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.15</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 14:40:32</t>
+          <t>09/29 11:25:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/28 18:19:39</t>
+          <t>09/29 13:06:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -217,7 +217,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31515.15</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>12048</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 11:25:36</t>
+          <t>09/30 08:30:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/29 13:06:13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>15476.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>15476.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/30 11:43:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15476</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>130000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15476.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15476</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15476.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 08:30:41</t>
+          <t>10/06 10:20:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>11627.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/30 11:43:33</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>15476</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>11627.91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15476</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>11627.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,183 +75,279 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/06 12:40:49</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9411.76</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/06 10:20:11</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11627.91</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>10/06 15:03:42</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20651</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>10/06 12:40:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>11627.91</t>
-        </is>
-      </c>
-    </row>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21039.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21039</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11627.91</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 12:40:49</t>
+          <t>10/12 11:06:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9411.76</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/06 10:20:11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11627.91</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/06 15:03:42</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20651</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/06 12:40:53</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11764.71</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>180000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21039.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21039</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.67</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/12 14:42:22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 11:06:33</t>
+          <t>10/15 11:12:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>190000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>22891.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/12 14:42:22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>190000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>22891.57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>22891.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/15 12:50:42</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16766.47</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/15 11:12:45</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>22891.57</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>190000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22891.57</t>
+          <t>330000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39658.03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>22891.57</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>39658.03</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 12:50:42</t>
+          <t>10/15 12:53:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16766.47</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10/15 12:50:42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16766.47</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>10/15 11:12:45</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>190000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>22891.57</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>330000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>39658.03</t>
+          <t>430000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51562.8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>39658.03</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>51562.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/15 14:16:29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>51562</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>430000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>51562.8</t>
+          <t>430000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51562.8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>51562</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>51562.8</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 12:34:20</t>
+          <t>10/18 16:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>10465.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/16 13:57:19</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>36585</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>10465.12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36585.37</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36585</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.37</t>
+          <t>10465.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/18 18:07:10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>40465</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>90000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10465.12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>40465</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10465.12</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-29999.88</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/18 18:07:10</t>
+          <t>10/18 18:07:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>10465</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-29999.88</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 16:50:27</t>
+          <t>10/19 11:01:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/18 18:07:35</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10465.12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10465</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.12</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/19 13:54:56</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15476.19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/19 11:01:06</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>12121.21</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27597.4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12121.21</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27597.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/19 15:44:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27597</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27597.4</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27597.4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27597</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>27597.4</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 13:54:56</t>
+          <t>10/20 13:42:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/19 11:01:06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12121.21</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/19 15:44:08</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>27597</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19393.94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27597.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>27597</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.4</t>
+          <t>19393.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/20 16:00:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19393</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19393.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19393</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19393.94</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 13:42:09</t>
+          <t>10/21 11:09:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>16626.51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/20 16:00:52</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>19393</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>138000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>16626.51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19393</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>16626.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/21 13:39:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16626</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>138000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>138000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16626.51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16626</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>16626.51</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/21 11:09:11</t>
+          <t>10/26 10:32:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>15457.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/21 13:39:36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16626</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>129840</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>15457.14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16626.51</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16626</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.51</t>
+          <t>15457.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/26 11:41:16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/26 10:32:43</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>129840</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15457.14</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>129840</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15457.14</t>
+          <t>429840</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51601.72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15457.14</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51601.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:41:16</t>
+          <t>10/26 13:26:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>128316</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>15275.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/26 10:32:43</t>
+          <t>10/26 11:41:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15457.14</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -257,7 +257,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>429840</t>
+          <t>428316</t>
         </is>
       </c>
     </row>
@@ -269,7 +269,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>51601.72</t>
+          <t>51420.29</t>
         </is>
       </c>
     </row>
@@ -293,7 +293,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51601.72</t>
+          <t>51420.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/26 13:29:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>51420</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>428316</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>51420.29</t>
+          <t>428316</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51420.29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51420</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>51420.29</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 13:26:45</t>
+          <t>10/28 13:18:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>128316</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15275.71</t>
+          <t>15476.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/26 11:41:16</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36144.58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/26 13:29:32</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>51420</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15476.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>428316</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>51420.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>51420</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.29</t>
+          <t>15476.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
+++ b/bills/JXZFSP01/-5253265175/8451cc887727b344dc36dcc396ae4dfb548a4dabad4e6050ee4ba5a2fac0c58b/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/28 15:01:09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15476</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15476.19</t>
+          <t>130000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15476.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15476</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15476.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>
